--- a/Date function.xlsx
+++ b/Date function.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f1c7af14bfcc0abe/Desktop/DA DS ITV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EACDA73-FD81-45E2-B0FA-CB8609F3B5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3EACDA73-FD81-45E2-B0FA-CB8609F3B5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3C748FD-81E0-44DA-A3AA-C01EC30CAEFD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Create from selection" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="227">
   <si>
     <t>Month</t>
   </si>
@@ -691,6 +691,30 @@
   </si>
   <si>
     <t>Retirement date(after 35 years)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joinung day name </t>
+  </si>
+  <si>
+    <t>Retirement month</t>
+  </si>
+  <si>
+    <t>Total delivery day</t>
+  </si>
+  <si>
+    <t>working day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today's Date </t>
+  </si>
+  <si>
+    <t>last day of delivery monyh</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>week day of delivery</t>
   </si>
 </sst>
 </file>
@@ -761,7 +785,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -875,11 +899,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -951,6 +1016,22 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1635,7 +1716,7 @@
       </c>
       <c r="G3" s="9">
         <f ca="1">NOW()</f>
-        <v>46289.811048148149</v>
+        <v>46289.976918518521</v>
       </c>
       <c r="H3" s="10">
         <v>46227.947916666664</v>
@@ -1755,7 +1836,7 @@
       </c>
       <c r="L5" s="9">
         <f ca="1">NOW()</f>
-        <v>46289.811048148149</v>
+        <v>46289.976918518521</v>
       </c>
       <c r="Q5" s="18"/>
       <c r="T5" s="29"/>
@@ -2463,29 +2544,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5C0CB30-5C6B-4798-B2DF-0A21E86F6020}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.77734375" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" customWidth="1"/>
     <col min="10" max="10" width="17.21875" customWidth="1"/>
     <col min="11" max="11" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.2">
+    <row r="1" spans="1:9" ht="31.2">
       <c r="A1" s="13" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="23.4">
+    <row r="3" spans="1:9" ht="23.4">
       <c r="A3" s="12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="43.2">
+    <row r="5" spans="1:9" ht="43.2">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -2507,8 +2589,14 @@
       <c r="G5" s="32" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="I5" s="36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2">
         <v>101</v>
       </c>
@@ -2529,9 +2617,20 @@
         <f ca="1">DATEDIF(C6,TODAY(),"Y")</f>
         <v>5</v>
       </c>
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="G6" s="18">
+        <f>EDATE(C6,35*12)</f>
+        <v>56994</v>
+      </c>
+      <c r="H6" t="str">
+        <f>TEXT(C6,"dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="I6" t="str">
+        <f>TEXT(G6,"mmmm")</f>
+        <v>January</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="2">
         <v>102</v>
       </c>
@@ -2552,8 +2651,20 @@
         <f t="shared" ref="F7:F10" ca="1" si="1">DATEDIF(C7,TODAY(),"Y")</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="G7" s="18">
+        <f t="shared" ref="G7:G10" si="2">EDATE(C7,35*12)</f>
+        <v>56673</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" ref="H7:H10" si="3">TEXT(C7,"dddd")</f>
+        <v>Friday</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" ref="I7:I10" si="4">TEXT(G7,"mmmm")</f>
+        <v>February</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="2">
         <v>103</v>
       </c>
@@ -2574,8 +2685,20 @@
         <f t="shared" ca="1" si="1"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="G8" s="18">
+        <f t="shared" si="2"/>
+        <v>56313</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="3"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="4"/>
+        <v>March</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2">
         <v>104</v>
       </c>
@@ -2596,8 +2719,20 @@
         <f t="shared" ca="1" si="1"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="G9" s="18">
+        <f t="shared" si="2"/>
+        <v>57452</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="3"/>
+        <v>Sunday</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="4"/>
+        <v>April</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2">
         <v>105</v>
       </c>
@@ -2618,30 +2753,45 @@
         <f t="shared" ca="1" si="1"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="18">
+      <c r="G10" s="18">
+        <f t="shared" si="2"/>
+        <v>56064</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="3"/>
+        <v>Friday</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="4"/>
+        <v>June</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="18.600000000000001" thickBot="1">
       <c r="A12" s="14" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9">
       <c r="A13" s="15"/>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="G13" s="34" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15" thickBot="1">
       <c r="A14" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="35">
         <f ca="1">TODAY()</f>
         <v>46289</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:9">
       <c r="A15" s="15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:9">
       <c r="A16" s="15" t="s">
         <v>117</v>
       </c>
@@ -2726,23 +2876,25 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6F2DCC1-8ED5-42B7-B182-90C462B3926A}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
+    <col min="6" max="6" width="22.77734375" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" customWidth="1"/>
     <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.2">
+    <row r="1" spans="1:8" ht="31.2">
       <c r="A1" s="13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="23.4">
+    <row r="3" spans="1:8" ht="23.4">
       <c r="A3" s="12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="28.8">
+    <row r="5" spans="1:8" ht="43.8" thickBot="1">
       <c r="A5" s="3" t="s">
         <v>123</v>
       </c>
@@ -2752,8 +2904,11 @@
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" s="41" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
         <v>125</v>
       </c>
@@ -2763,8 +2918,18 @@
       <c r="C6" s="7">
         <v>46224</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" s="20">
+        <f>WEEKDAY(C6)</f>
+        <v>3</v>
+      </c>
+      <c r="F6" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" thickBot="1">
       <c r="A7" s="2" t="s">
         <v>126</v>
       </c>
@@ -2774,8 +2939,20 @@
       <c r="C7" s="7">
         <v>46227</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="20">
+        <f t="shared" ref="D7:D10" si="0">WEEKDAY(C7)</f>
+        <v>6</v>
+      </c>
+      <c r="F7" s="38">
+        <f>COUNT(C6:C10)</f>
+        <v>5</v>
+      </c>
+      <c r="H7" s="38">
+        <f>NETWORKDAYS(B6,C10)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
         <v>127</v>
       </c>
@@ -2785,8 +2962,12 @@
       <c r="C8" s="7">
         <v>46231</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" thickBot="1">
       <c r="A9" s="2" t="s">
         <v>128</v>
       </c>
@@ -2796,8 +2977,12 @@
       <c r="C9" s="7">
         <v>46228</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" s="20">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" thickBot="1">
       <c r="A10" s="2" t="s">
         <v>129</v>
       </c>
@@ -2807,26 +2992,46 @@
       <c r="C10" s="7">
         <v>46232</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="18">
+      <c r="D10" s="20">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" thickBot="1">
+      <c r="F11" s="39">
+        <f>EOMONTH(C10,0)</f>
+        <v>46234</v>
+      </c>
+      <c r="G11" s="40" t="str">
+        <f>TEXT(F11,"dddd")</f>
+        <v>Friday</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18">
       <c r="A12" s="14" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:8">
       <c r="A13" s="15"/>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:8">
       <c r="A14" s="15" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:8">
       <c r="A15" s="15" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:8">
       <c r="A16" s="15" t="s">
         <v>132</v>
       </c>

--- a/Date function.xlsx
+++ b/Date function.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f1c7af14bfcc0abe/Desktop/DA DS ITV/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\OneDrive\Desktop\DA DS ITV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3EACDA73-FD81-45E2-B0FA-CB8609F3B5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3C748FD-81E0-44DA-A3AA-C01EC30CAEFD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A13B74-AFE2-437B-A5EA-AF32D024A87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Create from selection" sheetId="1" r:id="rId1"/>
@@ -944,7 +944,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1014,14 +1014,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1030,8 +1024,8 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1655,11 +1649,11 @@
       <c r="H1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
     </row>
     <row r="2" spans="1:26" ht="28.8">
       <c r="A2" s="2">
@@ -1682,14 +1676,14 @@
       </c>
       <c r="G2" s="19">
         <f ca="1">TODAY()</f>
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="H2" s="7">
         <v>46227</v>
       </c>
       <c r="O2">
         <f ca="1">WEEKNUM(TODAY())</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Z2" s="20" t="s">
         <v>216</v>
@@ -1716,7 +1710,7 @@
       </c>
       <c r="G3" s="9">
         <f ca="1">NOW()</f>
-        <v>46289.976918518521</v>
+        <v>46294.780425578705</v>
       </c>
       <c r="H3" s="10">
         <v>46227.947916666664</v>
@@ -1732,7 +1726,7 @@
       </c>
       <c r="O3">
         <f ca="1">WEEKDAY(TODAY())</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" s="24" t="s">
         <v>213</v>
@@ -1749,7 +1743,7 @@
       </c>
       <c r="Z3" s="22">
         <f ca="1">WORKDAY(TODAY(),7)</f>
-        <v>46300</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="43.2">
@@ -1773,7 +1767,7 @@
       </c>
       <c r="G4" s="11">
         <f ca="1">DAY(TODAY())</f>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H4" s="2">
         <v>15</v>
@@ -1786,7 +1780,7 @@
       </c>
       <c r="L4" s="8">
         <f ca="1">TODAY()</f>
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="T4" s="27">
         <v>46143</v>
@@ -1836,7 +1830,7 @@
       </c>
       <c r="L5" s="9">
         <f ca="1">NOW()</f>
-        <v>46289.976918518521</v>
+        <v>46294.780425578705</v>
       </c>
       <c r="Q5" s="18"/>
       <c r="T5" s="29"/>
@@ -1948,7 +1942,7 @@
       </c>
       <c r="G8" s="11">
         <f ca="1">WEEKNUM(TODAY())</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2">
         <v>3</v>
@@ -2069,7 +2063,7 @@
       </c>
       <c r="G10" s="11" t="str">
         <f ca="1">TEXT(TODAY(),"dddd")</f>
-        <v>Thursday</v>
+        <v>Tuesday</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>37</v>
@@ -2103,7 +2097,7 @@
       </c>
       <c r="T10" s="20">
         <f ca="1">TODAY()-S10</f>
-        <v>1389</v>
+        <v>1394</v>
       </c>
       <c r="U10" s="20" t="str">
         <f>TEXT(R10,"dddd")</f>
@@ -2275,7 +2269,7 @@
       </c>
       <c r="R14">
         <f ca="1">DATEDIF(O14,TODAY(),"YD")</f>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="T14" s="22">
         <f>EDATE(R10,240)</f>
@@ -2332,7 +2326,7 @@
       </c>
       <c r="R15">
         <f ca="1">DATEDIF(O15,TODAY(),"YD")</f>
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="57.6">
@@ -2589,10 +2583,10 @@
       <c r="G5" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="32" t="s">
         <v>220</v>
       </c>
     </row>
@@ -2773,7 +2767,7 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="15"/>
-      <c r="G13" s="34" t="s">
+      <c r="G13" s="33" t="s">
         <v>223</v>
       </c>
     </row>
@@ -2781,9 +2775,9 @@
       <c r="A14" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="34">
         <f ca="1">TODAY()</f>
-        <v>46289</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2904,7 +2898,7 @@
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="3" t="s">
         <v>226</v>
       </c>
     </row>
@@ -2922,10 +2916,10 @@
         <f>WEEKDAY(C6)</f>
         <v>3</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="35" t="s">
         <v>221</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="35" t="s">
         <v>222</v>
       </c>
     </row>
@@ -2943,11 +2937,11 @@
         <f t="shared" ref="D7:D10" si="0">WEEKDAY(C7)</f>
         <v>6</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="36">
         <f>COUNT(C6:C10)</f>
         <v>5</v>
       </c>
-      <c r="H7" s="38">
+      <c r="H7" s="36">
         <f>NETWORKDAYS(B6,C10)</f>
         <v>11</v>
       </c>
@@ -2996,19 +2990,19 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="F10" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="G10" s="33" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" thickBot="1">
-      <c r="F11" s="39">
+      <c r="F11" s="37">
         <f>EOMONTH(C10,0)</f>
         <v>46234</v>
       </c>
-      <c r="G11" s="40" t="str">
+      <c r="G11" s="38" t="str">
         <f>TEXT(F11,"dddd")</f>
         <v>Friday</v>
       </c>
@@ -3532,7 +3526,7 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.109375" customWidth="1"/>
     <col min="7" max="7" width="24.21875" customWidth="1"/>
   </cols>
